--- a/signup_forms/006_psa_form--signup_forms.xlsx
+++ b/signup_forms/006_psa_form--signup_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,10 +437,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
@@ -543,42 +543,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>media_declaration</t>
+          <t>swim_academy_details</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Media Declaration</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Please declare media that will be used by the swim academy.</t>
-        </is>
-      </c>
+          <t>Swim Academy Details</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>terms_and_conditions</t>
+          <t>media_declaration</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Terms and Conditions</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Media Declaration</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please declare media that will be used by the swim academy.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -588,7 +588,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -611,23 +611,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>swim_academy_details</t>
+          <t>swim_academy_website</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Swim Academy Details</t>
+          <t>Swim Academy Website</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -639,18 +639,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>kid_info_1</t>
+          <t>swim_academy_address</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kid</t>
+          <t>Swim Academy Address</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -662,12 +662,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kid_info_2</t>
+          <t>kid_info_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kid</t>
+          <t>Kid 1 Information</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -685,12 +685,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kid_info_3</t>
+          <t>kid_info_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kid</t>
+          <t>Kid 2 Information</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -708,12 +708,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>kid_info_4</t>
+          <t>kid_info_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kid</t>
+          <t>Kid 3 Information</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -731,16 +731,62 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>kid_info_5</t>
+          <t>kid_info_4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kid</t>
+          <t>Kid 4 Information</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>terms_and_conditions</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Terms and Conditions</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>kid_info_5</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Kid 5 Information</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -757,12 +803,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -785,153 +831,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>terms_and_conditions_choices</t>
+          <t>parent_agreement_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'agree',_'label':_'i_agree_to_the_terms_and_conditions'}</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'agree', 'label': 'I agree to the terms and conditions'}</t>
+          <t>I agree</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>terms_and_conditions_choices</t>
+          <t>parent_agreement_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'disagree',_'label':_'i_disagree'}</t>
+          <t>i_disagree</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'disagree', 'label': 'I disagree'}</t>
+          <t>I disagree</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>parent_agreement_choices</t>
+          <t>terms_and_conditions_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'agree',_'label':_'i_agree'}</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'agree', 'label': 'I agree'}</t>
+          <t>I agree</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>parent_agreement_choices</t>
+          <t>terms_and_conditions_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'disagree',_'label':_'i_disagree'}</t>
+          <t>i_disagree</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'disagree', 'label': 'I disagree'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>swim_academy_details_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'swim_academy_name',_'label':_'swim_academy_name'}</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'swim_academy_name', 'label': 'Swim Academy Name'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>swim_academy_details_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'swim_academy_phone',_'label':_'swim_academy_phone'}</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'swim_academy_phone', 'label': 'Swim Academy Phone'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>swim_academy_details_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'swim_academy_email',_'label':_'swim_academy_email'}</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'swim_academy_email', 'label': 'Swim Academy Email'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>swim_academy_details_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{'id':_4,_'name':_'swim_academy_address',_'label':_'swim_academy_address'}</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{'id': 4, 'name': 'swim_academy_address', 'label': 'Swim Academy Address'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>swim_academy_details_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'id':_5,_'name':_'swim_academy_website',_'label':_'swim_academy_website'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'id': 5, 'name': 'swim_academy_website', 'label': 'Swim Academy Website'}</t>
+          <t>I disagree</t>
         </is>
       </c>
     </row>
